--- a/artfynd/A 631-2025 artfynd.xlsx
+++ b/artfynd/A 631-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114333343</v>
+        <v>87348286</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korstorp, Vg</t>
+          <t>Rösslingen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435414</v>
+        <v>435373</v>
       </c>
       <c r="R2" t="n">
-        <v>6506740</v>
+        <v>6506799</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>1990-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+          <t>1990-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,55 +758,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Historiska artdata - hotade arter, Västra Götaland</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114333306</v>
+        <v>114333322</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +819,7 @@
         <v>435414</v>
       </c>
       <c r="R3" t="n">
-        <v>6506624</v>
+        <v>6506517</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,17 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
+          <t>alsumpskog, 1 exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,37 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114333344</v>
+        <v>114333340</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435407</v>
+        <v>435414</v>
       </c>
       <c r="R4" t="n">
-        <v>6506746</v>
+        <v>6506673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+          <t>bergsrygg ca 1 km s gården, äldre tallskog/mot hygge, ett exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114333305</v>
+        <v>110818113</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,37 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korstorp, Vg</t>
+          <t>Suntorp, Ö om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435414</v>
+        <v>435374</v>
       </c>
       <c r="R5" t="n">
-        <v>6506620</v>
+        <v>6506796</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,17 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,12 +1070,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1106,12 +1085,7 @@
         <v>114333255</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,15 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114333259</v>
+        <v>114333256</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,7 +1222,7 @@
         <v>435414</v>
       </c>
       <c r="R7" t="n">
-        <v>6506636</v>
+        <v>6506602</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114333345</v>
+        <v>114333257</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435404</v>
+        <v>435414</v>
       </c>
       <c r="R8" t="n">
-        <v>6506746</v>
+        <v>6506608</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,17 +1351,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+          <t>Korstorp åsryggen ca 800 meter s gården</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,15 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114333342</v>
+        <v>114333258</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1426,7 @@
         <v>435414</v>
       </c>
       <c r="R9" t="n">
-        <v>6506707</v>
+        <v>6506610</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1494,17 +1453,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+          <t>Korstorp åsryggen ca 800 meter s gården</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,15 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114333338</v>
+        <v>114333259</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1528,7 @@
         <v>435414</v>
       </c>
       <c r="R10" t="n">
-        <v>6506726</v>
+        <v>6506636</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1601,17 +1555,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+          <t>Korstorp åsryggen ca 800 meter s gården</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,37 +1592,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114333340</v>
+        <v>114333305</v>
       </c>
       <c r="B11" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102118</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,7 +1630,7 @@
         <v>435414</v>
       </c>
       <c r="R11" t="n">
-        <v>6506673</v>
+        <v>6506620</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1708,17 +1657,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>bergsrygg ca 1 km s gården, äldre tallskog/mot hygge, ett exemplar</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,15 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114333257</v>
+        <v>114333306</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,7 +1732,7 @@
         <v>435414</v>
       </c>
       <c r="R12" t="n">
-        <v>6506608</v>
+        <v>6506624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,17 +1759,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,37 +1796,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114333322</v>
+        <v>114333307</v>
       </c>
       <c r="B13" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,7 +1834,7 @@
         <v>435414</v>
       </c>
       <c r="R13" t="n">
-        <v>6506517</v>
+        <v>6506735</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1922,17 +1861,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>alsumpskog, 1 exemplar</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,15 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114333339</v>
+        <v>114333338</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +1936,7 @@
         <v>435414</v>
       </c>
       <c r="R14" t="n">
-        <v>6506730</v>
+        <v>6506726</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2066,15 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114333307</v>
+        <v>114333339</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2038,7 @@
         <v>435414</v>
       </c>
       <c r="R15" t="n">
-        <v>6506735</v>
+        <v>6506730</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2136,17 +2065,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården, rikligt</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,37 +2102,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114333301</v>
+        <v>114333342</v>
       </c>
       <c r="B16" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2216,7 +2140,7 @@
         <v>435414</v>
       </c>
       <c r="R16" t="n">
-        <v>6506690</v>
+        <v>6506707</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,17 +2167,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,15 +2204,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114333258</v>
+        <v>114333343</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2242,7 @@
         <v>435414</v>
       </c>
       <c r="R17" t="n">
-        <v>6506610</v>
+        <v>6506740</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2350,17 +2269,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,15 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114333256</v>
+        <v>114333344</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435414</v>
+        <v>435407</v>
       </c>
       <c r="R18" t="n">
-        <v>6506602</v>
+        <v>6506746</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2457,17 +2371,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Korstorp åsryggen ca 800 meter s gården</t>
+          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,6 +2405,210 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114333345</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>435404</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6506746</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Korstorp åsryggen ca 800 meter s gården, äldre tallskog, flertal exemplar</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114333301</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Korstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>435414</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6506690</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 631-2025 artfynd.xlsx
+++ b/artfynd/A 631-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>Historiska artdata - hotade arter, Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87348286</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333322</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110818113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333257</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333258</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333305</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333306</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333307</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333338</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333339</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333342</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333343</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333344</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2507,6 +2597,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333345</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,8 +2704,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114333301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>